--- a/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/BGC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_144329.xlsx
+++ b/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/BGC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_144329.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uetpk-my.sharepoint.com/personal/adeel_munir_uet_edu_pk/Documents/Drive G/Data science coding/VSCode programming/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3FEB30481562343A6CD35124C9BCF8369090F33C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_3FEB30481562343A6CD35124C9BCF8369090F33C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A4C49A-606D-4D1D-8D16-F6D3480AD27C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Original_Responses" sheetId="1" r:id="rId1"/>
@@ -1583,6 +1583,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3391,6 +3394,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="226.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">

--- a/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/BGC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_144329.xlsx
+++ b/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/BGC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_144329.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uetpk-my.sharepoint.com/personal/adeel_munir_uet_edu_pk/Documents/Drive G/Data science coding/VSCode programming/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_3FEB30481562343A6CD35124C9BCF8369090F33C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A4C49A-606D-4D1D-8D16-F6D3480AD27C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_3FEB30481562343A6CD35124C9BCF8369090F33C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2DD5DEB-9F10-4792-9092-515BC846A1D1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Original_Responses" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,19 @@
     <sheet name="15_BGC_Dimension_Themes" sheetId="15" r:id="rId15"/>
     <sheet name="16_Construct_Statistics" sheetId="16" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -40,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="203">
   <si>
     <t>Participant</t>
   </si>
@@ -646,13 +657,23 @@
   </si>
   <si>
     <t>Unmapped_Themes</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -678,14 +699,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3438,13 +3462,14 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>34.6</v>
+        <v>21</v>
+      </c>
+      <c r="E2" s="1">
+        <f>D2/26</f>
+        <v>0.80769230769230771</v>
       </c>
       <c r="F2" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="G2" t="s">
         <v>188</v>
@@ -3452,71 +3477,74 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>26.9</v>
+        <v>17</v>
+      </c>
+      <c r="E3" s="1">
+        <f>D3/26</f>
+        <v>0.65384615384615385</v>
       </c>
       <c r="F3" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C4">
         <v>12</v>
       </c>
       <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>19.2</v>
+        <v>15</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" ref="E3:E7" si="0">D4/26</f>
+        <v>0.57692307692307687</v>
       </c>
       <c r="F4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>19.2</v>
+        <v>14</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.53846153846153844</v>
       </c>
       <c r="F5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3530,13 +3558,14 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>19.2</v>
+        <v>11</v>
+      </c>
+      <c r="E6" s="1">
+        <f>D6/26</f>
+        <v>0.42307692307692307</v>
       </c>
       <c r="F6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G6" t="s">
         <v>192</v>
@@ -3553,10 +3582,11 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>3.8</v>
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.11538461538461539</v>
       </c>
       <c r="F7" t="s">
         <v>152</v>
@@ -3574,6 +3604,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
